--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2359-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2359-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B31A44CD-9BDE-43EF-9422-1B183EEC4DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B6318BF-BDB2-4F43-A8D0-C801415735D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{A0DD83CC-0C52-4A0A-A573-5EDCBAF81AB1}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{4612524C-9E88-448C-A5E7-8C797FF2CEED}"/>
   </bookViews>
   <sheets>
     <sheet name="2359-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1481,24 +1481,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB685475-F013-4625-B1AD-020D7DAEB4CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D3E0F9-3574-4147-91C8-5F93E76E0FBD}">
   <dimension ref="A1:R57"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1526,7 +1526,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1556,7 +1556,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1652,7 +1652,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2021</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2020</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2019</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>26</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>26</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2018</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2017</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2016</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2015</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>6.23</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2014</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2013</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2012</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2011</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2010</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2009</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2008</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2007</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2006</v>
       </c>
@@ -3794,7 +3794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2005</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2004</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2003</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>2002</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>2001</v>
       </c>
@@ -4064,7 +4064,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>2000</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>1999</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>1998</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>6.26</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>1997</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>2.23</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>1996</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39">
         <v>1995</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="37">
         <v>1994</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="39">
         <v>1993</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="37" t="s">
         <v>46</v>
       </c>
